--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260602.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260602.xlsx
@@ -975,17 +975,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>98,000</t>
+          <t>12,645,134</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>12,645,134</t>
+          <t>98,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>1,192,441</t>
+          <t>558,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1371,17 +1371,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>558,000</t>
+          <t>1,192,441</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>368,000</t>
+          <t>7,262,249</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>7,262,249</t>
+          <t>368,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>2,115,107</t>
+          <t>178,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>178,000</t>
+          <t>90,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>90,000</t>
+          <t>2,115,107</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>1,531,400</t>
+          <t>1,000,121</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>1,000,121</t>
+          <t>1,531,400</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>1,709,000</t>
+          <t>64,538</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>325,000</t>
+          <t>1,709,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>64,538</t>
+          <t>325,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
